--- a/site/StructureDefinition-hcen-service-request.xlsx
+++ b/site/StructureDefinition-hcen-service-request.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T01:23:13-03:00</t>
+    <t>2026-10-28T18:02:56-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -9221,7 +9221,7 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>20</v>
+        <v>523</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>20</v>
